--- a/data/input/Beneficio 2 - Gympass.xlsx
+++ b/data/input/Beneficio 2 - Gympass.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="139">
   <si>
     <t>Assinante</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Valor Desconto Coparticipação</t>
   </si>
   <si>
-    <t>Valor Mensal</t>
+    <t>Valor a pagar</t>
   </si>
   <si>
     <t>Adolfo Moreira</t>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Padrao 4 diarias</t>
+  </si>
+  <si>
+    <t>R$2000</t>
   </si>
   <si>
     <t>Adriana Nogueira</t>
@@ -517,7 +520,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -898,16 +901,16 @@
       <c r="H2" s="8">
         <v>0</v>
       </c>
-      <c r="I2" s="8">
-        <v>90</v>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="6">
         <v>44693</v>
@@ -933,16 +936,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6">
         <v>45485</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="7">
         <v>7</v>
@@ -962,10 +965,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="6">
         <v>45386</v>
@@ -991,10 +994,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6">
         <v>45163</v>
@@ -1020,10 +1023,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="9">
         <v>45645</v>
@@ -1049,10 +1052,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="6">
         <v>45069</v>
@@ -1078,10 +1081,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="6">
         <v>45554</v>
@@ -1107,10 +1110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="6">
         <v>45405</v>
@@ -1136,10 +1139,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="6">
         <v>45670</v>
@@ -1165,10 +1168,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6">
         <v>45628</v>
@@ -1194,16 +1197,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="6">
         <v>44693</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="7">
         <v>9</v>
@@ -1223,10 +1226,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="6">
         <v>44693</v>
@@ -1252,10 +1255,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="6">
         <v>45677</v>
@@ -1281,10 +1284,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="6">
         <v>44778</v>
@@ -1310,10 +1313,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="6">
         <v>45684</v>
@@ -1339,16 +1342,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="6">
         <v>45398</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" s="7">
         <v>10</v>
@@ -1368,10 +1371,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="9">
         <v>45646</v>
@@ -1397,10 +1400,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="9">
         <v>45655</v>
@@ -1426,16 +1429,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="6">
         <v>44693</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="7">
         <v>9</v>
@@ -1455,10 +1458,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="6">
         <v>44708</v>
@@ -1484,10 +1487,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="6">
         <v>44770</v>
@@ -1513,10 +1516,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="9">
         <v>44852</v>
@@ -1542,16 +1545,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="6">
         <v>44704</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" s="7">
         <v>9</v>
@@ -1571,10 +1574,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="6">
         <v>45629</v>
@@ -1600,10 +1603,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="9">
         <v>45583</v>
@@ -1629,16 +1632,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="6">
         <v>45510</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="7">
         <v>6</v>
@@ -1658,10 +1661,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="9">
         <v>45618</v>
@@ -1687,10 +1690,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="6">
         <v>45680</v>
@@ -1716,10 +1719,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="9">
         <v>44895</v>
@@ -1745,10 +1748,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="6">
         <v>45343</v>
@@ -1774,16 +1777,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="6">
         <v>45681</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E33" s="7">
         <v>1</v>
@@ -1803,10 +1806,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="6">
         <v>45378</v>
@@ -1832,10 +1835,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="6">
         <v>45383</v>
@@ -1861,16 +1864,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="6">
         <v>45552</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="7">
         <v>5</v>
@@ -1890,10 +1893,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="9">
         <v>44894</v>
@@ -1919,10 +1922,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="9">
         <v>45644</v>
@@ -1948,10 +1951,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="6">
         <v>45548</v>
@@ -1977,10 +1980,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" s="6">
         <v>45057</v>
@@ -2006,10 +2009,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C41" s="6">
         <v>44771</v>
@@ -2035,16 +2038,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="9">
         <v>45624</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E42" s="7">
         <v>3</v>
@@ -2064,10 +2067,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="6">
         <v>45163</v>
@@ -2093,10 +2096,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="6">
         <v>45687</v>
@@ -2122,10 +2125,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="6">
         <v>45603</v>
@@ -2151,10 +2154,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="6">
         <v>45526</v>
@@ -2180,16 +2183,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="6">
         <v>44704</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E47" s="7">
         <v>9</v>
@@ -2209,10 +2212,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C48" s="6">
         <v>45517</v>
@@ -2238,10 +2241,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C49" s="9">
         <v>45624</v>
@@ -2267,10 +2270,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" s="6">
         <v>44693</v>
@@ -2296,16 +2299,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C51" s="6">
         <v>44780</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E51" s="7">
         <v>6</v>
@@ -2325,10 +2328,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C52" s="6">
         <v>45465</v>
@@ -2354,10 +2357,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53" s="6">
         <v>45553</v>
@@ -2383,10 +2386,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C54" s="6">
         <v>44693</v>
@@ -2412,10 +2415,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C55" s="9">
         <v>44894</v>
@@ -2441,10 +2444,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C56" s="6">
         <v>45069</v>
@@ -2470,10 +2473,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" s="6">
         <v>45021</v>
@@ -2499,10 +2502,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="6">
         <v>45510</v>
@@ -2528,16 +2531,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C59" s="6">
         <v>45672</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E59" s="7">
         <v>1</v>
@@ -2557,10 +2560,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C60" s="6">
         <v>44720</v>
@@ -2586,10 +2589,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C61" s="6">
         <v>45327</v>
@@ -2615,10 +2618,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C62" s="6">
         <v>45426</v>
@@ -2644,10 +2647,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C63" s="6">
         <v>44713</v>
